--- a/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/d1_m7_tables_charts_answers.xlsx
+++ b/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/d1_m7_tables_charts_answers.xlsx
@@ -63,11 +63,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -374,23 +374,6 @@
 </wsDr>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OrdersTable" displayName="OrdersTable" ref="A1:H46" headerRowCount="1">
-  <autoFilter ref="A1:H46"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Order ID"/>
-    <tableColumn id="2" name="Order Date"/>
-    <tableColumn id="3" name="Customer"/>
-    <tableColumn id="4" name="Country"/>
-    <tableColumn id="5" name="Product"/>
-    <tableColumn id="6" name="Category"/>
-    <tableColumn id="7" name="Quantity"/>
-    <tableColumn id="8" name="Sales"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -693,43 +676,43 @@
     <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Order Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
@@ -741,7 +724,7 @@
           <t>O0001</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>46039</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -767,7 +750,7 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -777,7 +760,7 @@
           <t>O0002</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -803,8 +786,8 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>119.7</v>
+      <c r="H3" s="3" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -813,7 +796,7 @@
           <t>O0003</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -839,8 +822,8 @@
       <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>3332</v>
+      <c r="H4" s="3" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -849,7 +832,7 @@
           <t>O0004</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>46249</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -875,8 +858,8 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>1454.4</v>
+      <c r="H5" s="3" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -885,7 +868,7 @@
           <t>O0005</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>46123</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -911,8 +894,8 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>806</v>
+      <c r="H6" s="3" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -921,7 +904,7 @@
           <t>O0006</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -947,8 +930,8 @@
       <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <v>1656</v>
+      <c r="H7" s="3" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +940,7 @@
           <t>O0007</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>45458</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -983,8 +966,8 @@
       <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>326.25</v>
+      <c r="H8" s="3" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -993,7 +976,7 @@
           <t>O0008</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1019,8 +1002,8 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>779.2</v>
+      <c r="H9" s="3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1029,7 +1012,7 @@
           <t>O0009</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1055,8 +1038,8 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>587.2</v>
+      <c r="H10" s="3" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -1065,7 +1048,7 @@
           <t>O0010</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1091,8 +1074,8 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>801.6</v>
+      <c r="H11" s="3" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
@@ -1101,7 +1084,7 @@
           <t>O0011</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46317</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1127,8 +1110,8 @@
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>1663</v>
+      <c r="H12" s="3" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -1137,7 +1120,7 @@
           <t>O0012</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45857</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1163,8 +1146,8 @@
       <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>1037</v>
+      <c r="H13" s="3" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -1173,7 +1156,7 @@
           <t>O0013</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1199,8 +1182,8 @@
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>724</v>
+      <c r="H14" s="3" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1209,7 +1192,7 @@
           <t>O0014</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1235,8 +1218,8 @@
       <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>177</v>
+      <c r="H15" s="3" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1245,7 +1228,7 @@
           <t>O0015</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>46287</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1271,8 +1254,8 @@
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>653.8</v>
+      <c r="H16" s="3" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="17">
@@ -1281,7 +1264,7 @@
           <t>O0016</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>46107</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1307,8 +1290,8 @@
       <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>1758</v>
+      <c r="H17" s="3" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="18">
@@ -1317,7 +1300,7 @@
           <t>O0017</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1343,8 +1326,8 @@
       <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>56.1</v>
+      <c r="H18" s="3" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -1353,7 +1336,7 @@
           <t>O0018</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45508</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1379,8 +1362,8 @@
       <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>1148</v>
+      <c r="H19" s="3" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="20">
@@ -1389,7 +1372,7 @@
           <t>O0019</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1415,8 +1398,8 @@
       <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>905.25</v>
+      <c r="H20" s="3" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="21">
@@ -1425,7 +1408,7 @@
           <t>O0020</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1451,8 +1434,8 @@
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="n">
-        <v>918</v>
+      <c r="H21" s="3" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="22">
@@ -1461,7 +1444,7 @@
           <t>O0021</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1487,8 +1470,8 @@
       <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>1806.9</v>
+      <c r="H22" s="3" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="23">
@@ -1497,7 +1480,7 @@
           <t>O0022</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1523,8 +1506,8 @@
       <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="2" t="n">
-        <v>672.8</v>
+      <c r="H23" s="3" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="24">
@@ -1533,7 +1516,7 @@
           <t>O0023</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45522</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1559,8 +1542,8 @@
       <c r="G24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="2" t="n">
-        <v>619.4</v>
+      <c r="H24" s="3" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="25">
@@ -1569,7 +1552,7 @@
           <t>O0024</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46343</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1595,8 +1578,8 @@
       <c r="G25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>370</v>
+      <c r="H25" s="3" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1605,7 +1588,7 @@
           <t>O0025</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46363</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1631,8 +1614,8 @@
       <c r="G26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>882</v>
+      <c r="H26" s="3" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="27">
@@ -1641,7 +1624,7 @@
           <t>O0026</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1667,8 +1650,8 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>190.8</v>
+      <c r="H27" s="3" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1677,7 +1660,7 @@
           <t>O0027</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>46252</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1703,8 +1686,8 @@
       <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>1696</v>
+      <c r="H28" s="3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
@@ -1713,7 +1696,7 @@
           <t>O0028</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1739,8 +1722,8 @@
       <c r="G29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>102.2</v>
+      <c r="H29" s="3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -1749,7 +1732,7 @@
           <t>O0029</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1775,8 +1758,8 @@
       <c r="G30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="2" t="n">
-        <v>258.4</v>
+      <c r="H30" s="3" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="31">
@@ -1785,7 +1768,7 @@
           <t>O0030</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>46183</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1811,8 +1794,8 @@
       <c r="G31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="2" t="n">
-        <v>263</v>
+      <c r="H31" s="3" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1821,7 +1804,7 @@
           <t>O0031</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1847,8 +1830,8 @@
       <c r="G32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>159</v>
+      <c r="H32" s="3" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="33">
@@ -1857,7 +1840,7 @@
           <t>O0032</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1883,8 +1866,8 @@
       <c r="G33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="2" t="n">
-        <v>352</v>
+      <c r="H33" s="3" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="34">
@@ -1893,7 +1876,7 @@
           <t>O0033</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>46040</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1919,8 +1902,8 @@
       <c r="G34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="2" t="n">
-        <v>148</v>
+      <c r="H34" s="3" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="35">
@@ -1929,7 +1912,7 @@
           <t>O0034</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>45832</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -1955,8 +1938,8 @@
       <c r="G35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>226</v>
+      <c r="H35" s="3" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="36">
@@ -1965,7 +1948,7 @@
           <t>O0035</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>46343</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -1991,8 +1974,8 @@
       <c r="G36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="2" t="n">
-        <v>289.85</v>
+      <c r="H36" s="3" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="37">
@@ -2001,7 +1984,7 @@
           <t>O0036</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -2027,8 +2010,8 @@
       <c r="G37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>67</v>
+      <c r="H37" s="3" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="38">
@@ -2037,7 +2020,7 @@
           <t>O0037</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -2063,8 +2046,8 @@
       <c r="G38" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="2" t="n">
-        <v>4416</v>
+      <c r="H38" s="3" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="39">
@@ -2073,7 +2056,7 @@
           <t>O0038</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -2099,8 +2082,8 @@
       <c r="G39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="2" t="n">
-        <v>1160</v>
+      <c r="H39" s="3" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="40">
@@ -2109,7 +2092,7 @@
           <t>O0039</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -2135,8 +2118,8 @@
       <c r="G40" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="2" t="n">
-        <v>889.1</v>
+      <c r="H40" s="3" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="41">
@@ -2145,7 +2128,7 @@
           <t>O0040</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>46243</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2171,8 +2154,8 @@
       <c r="G41" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="2" t="n">
-        <v>115.9</v>
+      <c r="H41" s="3" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="42">
@@ -2181,7 +2164,7 @@
           <t>O0041</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2207,8 +2190,8 @@
       <c r="G42" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="n">
-        <v>303.05</v>
+      <c r="H42" s="3" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -2217,7 +2200,7 @@
           <t>O0042</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2243,8 +2226,8 @@
       <c r="G43" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="n">
-        <v>710</v>
+      <c r="H43" s="3" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="44">
@@ -2253,7 +2236,7 @@
           <t>O0043</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>46368</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2279,8 +2262,8 @@
       <c r="G44" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="2" t="n">
-        <v>1245</v>
+      <c r="H44" s="3" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="45">
@@ -2289,7 +2272,7 @@
           <t>O0044</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45538</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2315,8 +2298,8 @@
       <c r="G45" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="2" t="n">
-        <v>1009.6</v>
+      <c r="H45" s="3" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="46">
@@ -2325,7 +2308,7 @@
           <t>O0045</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45494</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2351,8 +2334,8 @@
       <c r="G46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="n">
-        <v>782</v>
+      <c r="H46" s="3" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -2381,9 +2364,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2401,12 +2381,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Sales</t>
         </is>
@@ -2418,7 +2398,7 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <f>SUMIF(Orders!F:F,A2,Orders!H:H)</f>
         <v/>
       </c>
@@ -2429,7 +2409,7 @@
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <f>SUMIF(Orders!F:F,A3,Orders!H:H)</f>
         <v/>
       </c>
@@ -2440,7 +2420,7 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <f>SUMIF(Orders!F:F,A4,Orders!H:H)</f>
         <v/>
       </c>
@@ -2451,7 +2431,7 @@
           <t>Accessory</t>
         </is>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <f>SUMIF(Orders!F:F,A5,Orders!H:H)</f>
         <v/>
       </c>
@@ -2462,7 +2442,7 @@
           <t>Smart Home</t>
         </is>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <f>SUMIF(Orders!F:F,A6,Orders!H:H)</f>
         <v/>
       </c>

--- a/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/d1_m7_tables_charts_answers.xlsx
+++ b/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/d1_m7_tables_charts_answers.xlsx
@@ -663,13 +663,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="19.5" customWidth="1" min="3" max="3"/>
-    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -883,19 +883,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7">
@@ -905,33 +905,33 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -941,33 +941,33 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45458</v>
+        <v>45922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45856</v>
+        <v>46084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45383</v>
+        <v>45796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1063,19 +1063,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12">
@@ -1085,33 +1085,33 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46317</v>
+        <v>46200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13">
@@ -1121,33 +1121,33 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45857</v>
+        <v>45944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45994</v>
+        <v>46365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1171,19 +1171,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="15">
@@ -1193,33 +1193,33 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45453</v>
+        <v>45682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
@@ -1229,33 +1229,33 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -1265,33 +1265,33 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46107</v>
+        <v>45734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -1301,33 +1301,33 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46011</v>
+        <v>46347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tatenda Mpofu</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45508</v>
+        <v>45902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45671</v>
+        <v>46065</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1387,16 +1387,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1400</v>
@@ -1409,11 +1409,11 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45306</v>
+        <v>45824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rutendo Chikafu</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1423,923 +1423,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>O0021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45939</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>O0022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>O0023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45522</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>O0024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>O0025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>46363</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>O0026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>O0027</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MacBook Air M4</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>O0028</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Laptop Sleeve 15in</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>O0029</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45498</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Bluetooth Headphones</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>O0030</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="3" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>O0031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45855</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nyasha Banda</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>USB-C Hub 7in1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>O0032</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>O0033</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>O0034</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45832</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>O0035</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Kagiso Molefe</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>O0036</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45481</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Wireless Mouse Pro</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>O0037</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>O0038</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45940</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>O0039</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>O0040</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>O0041</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45511</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>O0042</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>45676</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>O0043</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>46368</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>O0044</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>45538</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>O0045</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>45494</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Kagiso Molefe</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>iPhone 16</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H46">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -2351,7 +1451,7 @@
       <formula>1500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G46">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
